--- a/TestData/testdata.xlsx
+++ b/TestData/testdata.xlsx
@@ -16,24 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>admin@yourstore.com</t>
+    <t>mahesh</t>
   </si>
   <si>
-    <t>adm</t>
-  </si>
-  <si>
-    <t>adm@yourstore.com</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>${username}</t>
-  </si>
-  <si>
-    <t>${password}</t>
+    <t>username</t>
   </si>
 </sst>
 </file>
@@ -378,49 +366,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="A3" r:id="rId2"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
